--- a/VerveStacks_IND_grids_kan60/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_IND_grids_kan60/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan60\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3E148B-AF22-4A08-88AB-6E56AB35B971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403880C3-C0B9-43CD-B729-F15DB054141A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="12772" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -1146,10 +1146,10 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="N12" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="O12" t="s">
         <v>179</v>
@@ -1208,10 +1208,10 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>165</v>
+        <v>87</v>
       </c>
       <c r="N13" t="s">
-        <v>166</v>
+        <v>88</v>
       </c>
       <c r="O13" t="s">
         <v>179</v>
@@ -1332,10 +1332,10 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="N15" t="s">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="O15" t="s">
         <v>179</v>
@@ -1394,10 +1394,10 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="N16" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="O16" t="s">
         <v>179</v>
@@ -1456,10 +1456,10 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="N17" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="O17" t="s">
         <v>179</v>
@@ -1518,10 +1518,10 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="N18" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="O18" t="s">
         <v>179</v>
@@ -1580,10 +1580,10 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="N19" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="O19" t="s">
         <v>179</v>
@@ -1642,10 +1642,10 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="N20" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="O20" t="s">
         <v>179</v>
@@ -1704,10 +1704,10 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>90</v>
+        <v>154</v>
       </c>
       <c r="N21" t="s">
-        <v>91</v>
+        <v>155</v>
       </c>
       <c r="O21" t="s">
         <v>179</v>
@@ -1766,10 +1766,10 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="N22" t="s">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="O22" t="s">
         <v>179</v>
@@ -1828,10 +1828,10 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O23" t="s">
         <v>179</v>
@@ -1890,10 +1890,10 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="N24" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="O24" t="s">
         <v>179</v>
@@ -1952,10 +1952,10 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>98</v>
+        <v>162</v>
       </c>
       <c r="N25" t="s">
-        <v>99</v>
+        <v>163</v>
       </c>
       <c r="O25" t="s">
         <v>179</v>
@@ -2014,10 +2014,10 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="N26" t="s">
-        <v>143</v>
+        <v>97</v>
       </c>
       <c r="O26" t="s">
         <v>179</v>
@@ -2076,10 +2076,10 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="N27" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="O27" t="s">
         <v>179</v>
@@ -2138,10 +2138,10 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="N28" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="O28" t="s">
         <v>179</v>
@@ -2200,10 +2200,10 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="N29" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="O29" t="s">
         <v>179</v>
@@ -2262,10 +2262,10 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="N30" t="s">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="O30" t="s">
         <v>179</v>
@@ -2324,10 +2324,10 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="N31" t="s">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="O31" t="s">
         <v>179</v>
@@ -2386,10 +2386,10 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N32" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O32" t="s">
         <v>179</v>
@@ -2448,10 +2448,10 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="N33" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="O33" t="s">
         <v>179</v>
@@ -2510,10 +2510,10 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="N34" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="O34" t="s">
         <v>179</v>
@@ -2572,10 +2572,10 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="N35" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="O35" t="s">
         <v>179</v>
@@ -2634,10 +2634,10 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N36" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="O36" t="s">
         <v>179</v>
@@ -2696,10 +2696,10 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>104</v>
+        <v>177</v>
       </c>
       <c r="N37" t="s">
-        <v>105</v>
+        <v>178</v>
       </c>
       <c r="O37" t="s">
         <v>179</v>
@@ -2758,10 +2758,10 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="N38" t="s">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="O38" t="s">
         <v>179</v>
@@ -2820,10 +2820,10 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>173</v>
+        <v>120</v>
       </c>
       <c r="N39" t="s">
-        <v>174</v>
+        <v>121</v>
       </c>
       <c r="O39" t="s">
         <v>179</v>
@@ -2882,10 +2882,10 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>116</v>
+        <v>167</v>
       </c>
       <c r="N40" t="s">
-        <v>117</v>
+        <v>168</v>
       </c>
       <c r="O40" t="s">
         <v>179</v>
@@ -2944,10 +2944,10 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>152</v>
+        <v>98</v>
       </c>
       <c r="N41" t="s">
-        <v>153</v>
+        <v>99</v>
       </c>
       <c r="O41" t="s">
         <v>179</v>
@@ -3006,10 +3006,10 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>162</v>
+        <v>106</v>
       </c>
       <c r="N42" t="s">
-        <v>163</v>
+        <v>107</v>
       </c>
       <c r="O42" t="s">
         <v>179</v>
@@ -3068,10 +3068,10 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="N43" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="O43" t="s">
         <v>179</v>
@@ -3106,10 +3106,10 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="N44" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="O44" t="s">
         <v>179</v>
@@ -3144,10 +3144,10 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>177</v>
+        <v>124</v>
       </c>
       <c r="N45" t="s">
-        <v>178</v>
+        <v>125</v>
       </c>
       <c r="O45" t="s">
         <v>179</v>
@@ -3182,10 +3182,10 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>87</v>
+        <v>175</v>
       </c>
       <c r="N46" t="s">
-        <v>88</v>
+        <v>176</v>
       </c>
       <c r="O46" t="s">
         <v>179</v>
@@ -3220,10 +3220,10 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>175</v>
+        <v>112</v>
       </c>
       <c r="N47" t="s">
-        <v>176</v>
+        <v>113</v>
       </c>
       <c r="O47" t="s">
         <v>179</v>
@@ -3258,10 +3258,10 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="N48" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="O48" t="s">
         <v>179</v>
@@ -3284,10 +3284,10 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="N49" t="s">
-        <v>168</v>
+        <v>123</v>
       </c>
       <c r="O49" t="s">
         <v>179</v>
@@ -3310,10 +3310,10 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>171</v>
+        <v>114</v>
       </c>
       <c r="N50" t="s">
-        <v>172</v>
+        <v>115</v>
       </c>
       <c r="O50" t="s">
         <v>179</v>
@@ -3336,10 +3336,10 @@
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="N51" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="O51" t="s">
         <v>179</v>
@@ -3362,10 +3362,10 @@
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>106</v>
+        <v>169</v>
       </c>
       <c r="N52" t="s">
-        <v>107</v>
+        <v>170</v>
       </c>
       <c r="O52" t="s">
         <v>179</v>
@@ -3388,10 +3388,10 @@
         <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="N53" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="O53" t="s">
         <v>179</v>
@@ -3440,10 +3440,10 @@
         <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>156</v>
+        <v>94</v>
       </c>
       <c r="N55" t="s">
-        <v>157</v>
+        <v>95</v>
       </c>
       <c r="O55" t="s">
         <v>179</v>

--- a/VerveStacks_IND_grids_kan60/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_IND_grids_kan60/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan60\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403880C3-C0B9-43CD-B729-F15DB054141A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1E344B-3C61-43E6-B468-1BA2D2274CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12773" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -1084,10 +1084,10 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="N11" t="s">
-        <v>145</v>
+        <v>97</v>
       </c>
       <c r="O11" t="s">
         <v>179</v>
@@ -1146,10 +1146,10 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="N12" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="O12" t="s">
         <v>179</v>
@@ -1208,10 +1208,10 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>87</v>
+        <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>88</v>
+        <v>139</v>
       </c>
       <c r="O13" t="s">
         <v>179</v>
@@ -1270,10 +1270,10 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="N14" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="O14" t="s">
         <v>179</v>
@@ -1332,10 +1332,10 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="O15" t="s">
         <v>179</v>
@@ -1394,10 +1394,10 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="N16" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="O16" t="s">
         <v>179</v>
@@ -1456,10 +1456,10 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="N17" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="O17" t="s">
         <v>179</v>
@@ -1518,10 +1518,10 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="N18" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="O18" t="s">
         <v>179</v>
@@ -1580,10 +1580,10 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="N19" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="O19" t="s">
         <v>179</v>
@@ -1642,10 +1642,10 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="N20" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="O20" t="s">
         <v>179</v>
@@ -1704,10 +1704,10 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="N21" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="O21" t="s">
         <v>179</v>
@@ -1766,10 +1766,10 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="O22" t="s">
         <v>179</v>
@@ -1828,10 +1828,10 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="N23" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="O23" t="s">
         <v>179</v>
@@ -1890,10 +1890,10 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="N24" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="O24" t="s">
         <v>179</v>
@@ -1952,10 +1952,10 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>162</v>
+        <v>94</v>
       </c>
       <c r="N25" t="s">
-        <v>163</v>
+        <v>95</v>
       </c>
       <c r="O25" t="s">
         <v>179</v>
@@ -2014,10 +2014,10 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>96</v>
+        <v>162</v>
       </c>
       <c r="N26" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="O26" t="s">
         <v>179</v>
@@ -2076,10 +2076,10 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="N27" t="s">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="O27" t="s">
         <v>179</v>
@@ -2138,10 +2138,10 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="N28" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="O28" t="s">
         <v>179</v>
@@ -2200,10 +2200,10 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="N29" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="O29" t="s">
         <v>179</v>
@@ -2262,10 +2262,10 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="N30" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="O30" t="s">
         <v>179</v>
@@ -2324,10 +2324,10 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="N31" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="O31" t="s">
         <v>179</v>
@@ -2386,10 +2386,10 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="N32" t="s">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="O32" t="s">
         <v>179</v>
@@ -2448,10 +2448,10 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="N33" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="O33" t="s">
         <v>179</v>
@@ -2510,10 +2510,10 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="N34" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="O34" t="s">
         <v>179</v>
@@ -2572,10 +2572,10 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="N35" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="O35" t="s">
         <v>179</v>
@@ -2634,10 +2634,10 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="N36" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="O36" t="s">
         <v>179</v>
@@ -2696,10 +2696,10 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>177</v>
+        <v>150</v>
       </c>
       <c r="N37" t="s">
-        <v>178</v>
+        <v>151</v>
       </c>
       <c r="O37" t="s">
         <v>179</v>
@@ -2758,10 +2758,10 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="N38" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="O38" t="s">
         <v>179</v>
@@ -2820,10 +2820,10 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="N39" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="O39" t="s">
         <v>179</v>
@@ -2882,10 +2882,10 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>167</v>
+        <v>118</v>
       </c>
       <c r="N40" t="s">
-        <v>168</v>
+        <v>119</v>
       </c>
       <c r="O40" t="s">
         <v>179</v>
@@ -2944,10 +2944,10 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="N41" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="O41" t="s">
         <v>179</v>
@@ -3006,10 +3006,10 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>106</v>
+        <v>175</v>
       </c>
       <c r="N42" t="s">
-        <v>107</v>
+        <v>176</v>
       </c>
       <c r="O42" t="s">
         <v>179</v>
@@ -3068,10 +3068,10 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="N43" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="O43" t="s">
         <v>179</v>
@@ -3106,10 +3106,10 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="N44" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="O44" t="s">
         <v>179</v>
@@ -3144,10 +3144,10 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="N45" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="O45" t="s">
         <v>179</v>
@@ -3182,10 +3182,10 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="N46" t="s">
-        <v>176</v>
+        <v>125</v>
       </c>
       <c r="O46" t="s">
         <v>179</v>
@@ -3220,10 +3220,10 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="N47" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O47" t="s">
         <v>179</v>
@@ -3258,10 +3258,10 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="N48" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="O48" t="s">
         <v>179</v>
@@ -3284,10 +3284,10 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="N49" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="O49" t="s">
         <v>179</v>
@@ -3336,10 +3336,10 @@
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="N51" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="O51" t="s">
         <v>179</v>
@@ -3388,10 +3388,10 @@
         <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="N53" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="O53" t="s">
         <v>179</v>
@@ -3414,10 +3414,10 @@
         <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="N54" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="O54" t="s">
         <v>179</v>
@@ -3440,10 +3440,10 @@
         <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="N55" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="O55" t="s">
         <v>179</v>
